--- a/Test Results/Excel/Summary_Report.xlsx
+++ b/Test Results/Excel/Summary_Report.xlsx
@@ -26,25 +26,25 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="Arial"/>
+      <name val="Calibri"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
       <sz val="14"/>
     </font>
     <font>
-      <name val="Arial"/>
+      <name val="Calibri"/>
       <i val="1"/>
       <color rgb="00475569"/>
       <sz val="9"/>
     </font>
     <font>
-      <name val="Arial"/>
+      <name val="Calibri"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
       <sz val="10"/>
     </font>
     <font>
-      <name val="Arial"/>
+      <name val="Calibri"/>
       <color rgb="001F2937"/>
       <sz val="9.5"/>
     </font>
@@ -580,7 +580,7 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>27.24 seconds</t>
+          <t>71.15 seconds</t>
         </is>
       </c>
     </row>
